--- a/dados_solar.xlsx
+++ b/dados_solar.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.ivo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221696E1-BD4E-419B-AB6A-740B646BFFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB3BF3F-A720-46CD-9EED-0A2F9F09B812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCD1A57-B646-4411-BD8E-29B5C52B476E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{3BCD1A57-B646-4411-BD8E-29B5C52B476E}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensal" sheetId="2" r:id="rId1"/>
     <sheet name="Diario" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="14">
   <si>
     <t>Usina</t>
   </si>
@@ -85,6 +85,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -126,10 +129,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,17 +508,17 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>163.63999999999999</v>
-      </c>
-      <c r="C2">
-        <v>174.16</v>
+      <c r="B2" s="3">
+        <v>161.34709000000001</v>
+      </c>
+      <c r="C2" s="3">
+        <v>166.64672487938839</v>
       </c>
       <c r="D2">
-        <v>93.96</v>
-      </c>
-      <c r="E2">
-        <v>5.66</v>
+        <v>0.96819838563749738</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2.82</v>
       </c>
       <c r="F2">
         <v>0.4</v>
@@ -526,20 +531,20 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>170.57</v>
-      </c>
-      <c r="C3">
-        <v>175.67</v>
+      <c r="B3" s="3">
+        <v>166.61199999999999</v>
+      </c>
+      <c r="C3" s="3">
+        <v>163.15379147478086</v>
       </c>
       <c r="D3">
-        <v>97.09</v>
+        <v>1.0211960046650443</v>
       </c>
       <c r="E3">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -549,43 +554,43 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>381.44</v>
-      </c>
-      <c r="C4">
-        <v>446.2</v>
+      <c r="B4" s="3">
+        <v>387.41209999999995</v>
+      </c>
+      <c r="C4" s="3">
+        <v>414.9</v>
       </c>
       <c r="D4">
-        <v>85.49</v>
+        <v>0.93374813208001917</v>
       </c>
       <c r="E4">
-        <v>8.8699999999999992</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F4">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G4">
-        <v>4.5999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>402.7</v>
-      </c>
-      <c r="C5">
-        <v>442.8</v>
+      <c r="B5" s="3">
+        <v>383.28990000000005</v>
+      </c>
+      <c r="C5" s="3">
+        <v>405.7</v>
       </c>
       <c r="D5">
-        <v>90.94</v>
+        <v>0.94476189302440239</v>
       </c>
       <c r="E5">
-        <v>7.19</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F5">
-        <v>1.1000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G5">
         <v>0.8</v>
@@ -598,7 +603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CD6D3C-908B-4AAE-83CF-8D410A2BF6FA}">
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -623,1738 +628,1801 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>6.26396</v>
+        <v>3.7030000000000007</v>
       </c>
       <c r="D2">
-        <v>4.6500000000000004</v>
+        <v>2.7450000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46083</v>
+        <f>A2+1</f>
+        <v>46114</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>6.9431599999999998</v>
+        <v>4.1284999999999998</v>
       </c>
       <c r="D3">
-        <v>5.508</v>
+        <v>3.2410000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46084</v>
+        <f t="shared" ref="A4:A31" si="0">A3+1</f>
+        <v>46115</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>5.7449899999999996</v>
+        <v>3.6462200000000005</v>
       </c>
       <c r="D4">
-        <v>4.4720000000000004</v>
+        <v>2.7189999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46085</v>
+        <f t="shared" si="0"/>
+        <v>46116</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>4.8886599999999998</v>
+        <v>5.5127900000000007</v>
       </c>
       <c r="D5">
-        <v>4.3079999999999998</v>
+        <v>4.0069999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46086</v>
+        <f t="shared" si="0"/>
+        <v>46117</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>6.5501400000000007</v>
+        <v>5.325120000000001</v>
       </c>
       <c r="D6">
-        <v>5.0019999999999998</v>
+        <v>3.5350000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46087</v>
+        <f t="shared" si="0"/>
+        <v>46118</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>5.3411999999999997</v>
+        <v>4.6341200000000002</v>
       </c>
       <c r="D7">
-        <v>4.3730000000000002</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46088</v>
+        <f t="shared" si="0"/>
+        <v>46119</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>4.0292299999999992</v>
+        <v>4.4261800000000004</v>
       </c>
       <c r="D8">
-        <v>3.3479999999999999</v>
+        <v>3.298</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46089</v>
+        <f t="shared" si="0"/>
+        <v>46120</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>4.1196999999999999</v>
+        <v>5.2195299999999998</v>
       </c>
       <c r="D9">
-        <v>3.6469999999999998</v>
+        <v>3.9089999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46090</v>
+        <f t="shared" si="0"/>
+        <v>46121</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>5.6862399999999997</v>
+        <v>4.8653499999999994</v>
       </c>
       <c r="D10">
-        <v>5.0170000000000003</v>
+        <v>3.7229999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46091</v>
+        <f t="shared" si="0"/>
+        <v>46122</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>5.3296099999999997</v>
+        <v>5.8116199999999987</v>
       </c>
       <c r="D11">
-        <v>4.4960000000000004</v>
+        <v>4.2759999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46092</v>
+        <f t="shared" si="0"/>
+        <v>46123</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>3.7745500000000001</v>
+        <v>6.7245700000000008</v>
       </c>
       <c r="D12">
-        <v>3.044</v>
+        <v>4.867</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46093</v>
+        <f t="shared" si="0"/>
+        <v>46124</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>2.8529899999999997</v>
+        <v>5.9699200000000001</v>
       </c>
       <c r="D13">
-        <v>2.31</v>
+        <v>4.1680000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46094</v>
+        <f t="shared" si="0"/>
+        <v>46125</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>6.5708199999999994</v>
+        <v>5.1132399999999993</v>
       </c>
       <c r="D14">
-        <v>5.12</v>
+        <v>3.677</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46095</v>
+        <f t="shared" si="0"/>
+        <v>46126</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>3.3125100000000001</v>
+        <v>5.7803000000000004</v>
       </c>
       <c r="D15">
-        <v>2.6459999999999999</v>
+        <v>4.2590000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46096</v>
+        <f t="shared" si="0"/>
+        <v>46127</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>5.3719999999999999</v>
+        <v>3.8199800000000002</v>
       </c>
       <c r="D16">
-        <v>4.641</v>
+        <v>2.6749999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46097</v>
+        <f t="shared" si="0"/>
+        <v>46128</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>6.3389999999999995</v>
+        <v>4.6476899999999999</v>
       </c>
       <c r="D17">
-        <v>5.2709999999999999</v>
+        <v>3.3650000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46098</v>
+        <f t="shared" si="0"/>
+        <v>46129</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>3.5692499999999998</v>
+        <v>3.9472499999999999</v>
       </c>
       <c r="D18">
-        <v>2.8849999999999998</v>
+        <v>2.7869999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46099</v>
+        <f t="shared" si="0"/>
+        <v>46130</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>4.2707899999999999</v>
+        <v>5.9527799999999997</v>
       </c>
       <c r="D19">
-        <v>3.0390000000000001</v>
+        <v>3.8239999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46100</v>
+        <f t="shared" si="0"/>
+        <v>46131</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>6.5658599999999989</v>
+        <v>6.8549300000000004</v>
       </c>
       <c r="D20">
-        <v>4.9320000000000004</v>
+        <v>4.8129999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46101</v>
+        <f t="shared" si="0"/>
+        <v>46132</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>4.0144100000000007</v>
+        <v>5.3584499999999995</v>
       </c>
       <c r="D21">
-        <v>3.1920000000000002</v>
+        <v>3.778</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46102</v>
+        <f t="shared" si="0"/>
+        <v>46133</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>5.9600300000000006</v>
+        <v>5.0553400000000002</v>
       </c>
       <c r="D22">
-        <v>4.415</v>
+        <v>3.6909999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46103</v>
+        <f t="shared" si="0"/>
+        <v>46134</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>5.85602</v>
+        <v>5.714900000000001</v>
       </c>
       <c r="D23">
-        <v>4.1390000000000002</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46104</v>
+        <f t="shared" si="0"/>
+        <v>46135</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>6.2333999999999996</v>
+        <v>5.9154299999999997</v>
       </c>
       <c r="D24">
-        <v>5.2119999999999997</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46105</v>
+        <f t="shared" si="0"/>
+        <v>46136</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>5.7830600000000016</v>
+        <v>6.2084299999999999</v>
       </c>
       <c r="D25">
-        <v>4.8079999999999998</v>
+        <v>4.2469999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46106</v>
+        <f t="shared" si="0"/>
+        <v>46137</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>5.3223200000000004</v>
+        <v>6.2420900000000001</v>
       </c>
       <c r="D26">
-        <v>4.2220000000000004</v>
+        <v>3.931</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46107</v>
+        <f t="shared" si="0"/>
+        <v>46138</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>3.5502899999999999</v>
+        <v>6.4459900000000001</v>
       </c>
       <c r="D27">
-        <v>2.5270000000000001</v>
+        <v>4.3099999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46108</v>
+        <f t="shared" si="0"/>
+        <v>46139</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>6.08291</v>
+        <v>4.2450199999999993</v>
       </c>
       <c r="D28">
-        <v>4.101</v>
+        <v>3.1549999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46109</v>
+        <f t="shared" si="0"/>
+        <v>46140</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>6.5620700000000003</v>
+        <v>6.2449399999999997</v>
       </c>
       <c r="D29">
-        <v>4.97</v>
+        <v>3.8679999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46110</v>
+        <f t="shared" si="0"/>
+        <v>46141</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>4.7931200000000009</v>
+        <v>6.8811800000000005</v>
       </c>
       <c r="D30">
-        <v>3.51</v>
+        <v>4.4169999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46111</v>
+        <f t="shared" si="0"/>
+        <v>46142</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>7.149210000000001</v>
+        <v>6.9522300000000001</v>
       </c>
       <c r="D31">
-        <v>5.2190000000000003</v>
+        <v>4.391</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46112</v>
+        <f>A2</f>
+        <v>46113</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>4.8068099999999996</v>
+        <v>3.7586999999999509</v>
       </c>
       <c r="D32">
-        <v>3.5179999999999998</v>
+        <v>2.7450000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46082</v>
+        <f t="shared" ref="A33:A96" si="1">A3</f>
+        <v>46114</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33">
-        <v>6.855800000000043</v>
+        <v>4.2283999999999606</v>
       </c>
       <c r="D33">
-        <v>4.6500000000000004</v>
+        <v>3.2410000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46083</v>
+        <f t="shared" si="1"/>
+        <v>46115</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
       </c>
       <c r="C34">
-        <v>7.1727999999999277</v>
+        <v>4.0794999999999382</v>
       </c>
       <c r="D34">
-        <v>5.508</v>
+        <v>2.7189999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46084</v>
+        <f t="shared" si="1"/>
+        <v>46116</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
       </c>
       <c r="C35">
-        <v>6.1791000000000302</v>
+        <v>5.7499000000000198</v>
       </c>
       <c r="D35">
-        <v>4.4720000000000004</v>
+        <v>4.0069999999999997</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46085</v>
+        <f t="shared" si="1"/>
+        <v>46117</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36">
-        <v>4.95019999999995</v>
+        <v>5.8331000000000879</v>
       </c>
       <c r="D36">
-        <v>4.3079999999999998</v>
+        <v>3.5350000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46086</v>
+        <f t="shared" si="1"/>
+        <v>46118</v>
       </c>
       <c r="B37" t="s">
         <v>3</v>
       </c>
       <c r="C37">
-        <v>6.9408999999999619</v>
+        <v>4.9960999999999736</v>
       </c>
       <c r="D37">
-        <v>5.0019999999999998</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46087</v>
+        <f t="shared" si="1"/>
+        <v>46119</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
       </c>
       <c r="C38">
-        <v>5.8134000000000761</v>
+        <v>4.5902999999999263</v>
       </c>
       <c r="D38">
-        <v>4.3730000000000002</v>
+        <v>3.298</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46088</v>
+        <f t="shared" si="1"/>
+        <v>46120</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39">
-        <v>4.4488999999999024</v>
+        <v>5.2613000000001593</v>
       </c>
       <c r="D39">
-        <v>3.3479999999999999</v>
+        <v>3.9089999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46089</v>
+        <f t="shared" si="1"/>
+        <v>46121</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
       </c>
       <c r="C40">
-        <v>4.3962000000000083</v>
+        <v>4.903499999999938</v>
       </c>
       <c r="D40">
-        <v>3.6469999999999998</v>
+        <v>3.7229999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46090</v>
+        <f t="shared" si="1"/>
+        <v>46122</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>5.8588000000000404</v>
+        <v>5.6732999999999825</v>
       </c>
       <c r="D41">
-        <v>5.0170000000000003</v>
+        <v>4.2759999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46091</v>
+        <f t="shared" si="1"/>
+        <v>46123</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>5.3564999999999374</v>
+        <v>6.8532999999999848</v>
       </c>
       <c r="D42">
-        <v>4.4960000000000004</v>
+        <v>4.867</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46092</v>
+        <f t="shared" si="1"/>
+        <v>46124</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>4.256900000000134</v>
+        <v>6.0750999999999156</v>
       </c>
       <c r="D43">
-        <v>3.044</v>
+        <v>4.1680000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46093</v>
+        <f t="shared" si="1"/>
+        <v>46125</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
       </c>
       <c r="C44">
-        <v>3.0779999999998799</v>
+        <v>5.0581000000000298</v>
       </c>
       <c r="D44">
-        <v>2.31</v>
+        <v>3.677</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46094</v>
+        <f t="shared" si="1"/>
+        <v>46126</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>6.7439999999999962</v>
+        <v>5.7979000000001362</v>
       </c>
       <c r="D45">
-        <v>5.12</v>
+        <v>4.2590000000000003</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46095</v>
+        <f t="shared" si="1"/>
+        <v>46127</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>3.5999000000000207</v>
+        <v>4.0025999999999993</v>
       </c>
       <c r="D46">
-        <v>2.6459999999999999</v>
+        <v>2.6749999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46096</v>
+        <f t="shared" si="1"/>
+        <v>46128</v>
       </c>
       <c r="B47" t="s">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>5.5045999999999733</v>
+        <v>4.7296000000000333</v>
       </c>
       <c r="D47">
-        <v>4.641</v>
+        <v>3.3650000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46097</v>
+        <f t="shared" si="1"/>
+        <v>46129</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>6.3954000000000759</v>
+        <v>4.1324999999998804</v>
       </c>
       <c r="D48">
-        <v>5.2709999999999999</v>
+        <v>2.7869999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46098</v>
+        <f t="shared" si="1"/>
+        <v>46130</v>
       </c>
       <c r="B49" t="s">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>3.6752999999999849</v>
+        <v>6.4274999999999967</v>
       </c>
       <c r="D49">
-        <v>2.8849999999999998</v>
+        <v>3.8239999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46099</v>
+        <f t="shared" si="1"/>
+        <v>46131</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>4.727399999999963</v>
+        <v>7.1028999999999627</v>
       </c>
       <c r="D50">
-        <v>3.0390000000000001</v>
+        <v>4.8129999999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46100</v>
+        <f t="shared" si="1"/>
+        <v>46132</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>6.6707000000000081</v>
+        <v>5.4603000000000428</v>
       </c>
       <c r="D51">
-        <v>4.9320000000000004</v>
+        <v>3.778</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46101</v>
+        <f t="shared" si="1"/>
+        <v>46133</v>
       </c>
       <c r="B52" t="s">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>4.1962000000000668</v>
+        <v>5.1278000000000992</v>
       </c>
       <c r="D52">
-        <v>3.1920000000000002</v>
+        <v>3.6909999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46102</v>
+        <f t="shared" si="1"/>
+        <v>46134</v>
       </c>
       <c r="B53" t="s">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>6.3074999999999974</v>
+        <v>6.0178999999999618</v>
       </c>
       <c r="D53">
-        <v>4.415</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46103</v>
+        <f t="shared" si="1"/>
+        <v>46135</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>6.0481000000000327</v>
+        <v>5.9982999999999267</v>
       </c>
       <c r="D54">
-        <v>4.1390000000000002</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46104</v>
+        <f t="shared" si="1"/>
+        <v>46136</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
       </c>
       <c r="C55">
-        <v>6.4399999999998805</v>
+        <v>6.2139999999999969</v>
       </c>
       <c r="D55">
-        <v>5.2119999999999997</v>
+        <v>4.2469999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46105</v>
+        <f t="shared" si="1"/>
+        <v>46137</v>
       </c>
       <c r="B56" t="s">
         <v>3</v>
       </c>
       <c r="C56">
-        <v>5.7172999999999865</v>
+        <v>6.5604999999999958</v>
       </c>
       <c r="D56">
-        <v>4.8079999999999998</v>
+        <v>3.931</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46106</v>
+        <f t="shared" si="1"/>
+        <v>46138</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57">
-        <v>5.3851000000000306</v>
+        <v>6.6729000000000198</v>
       </c>
       <c r="D57">
-        <v>4.2220000000000004</v>
+        <v>4.3099999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46107</v>
+        <f t="shared" si="1"/>
+        <v>46139</v>
       </c>
       <c r="B58" t="s">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>3.9011000000000307</v>
+        <v>4.3111000000000326</v>
       </c>
       <c r="D58">
-        <v>2.5270000000000001</v>
+        <v>3.1549999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46108</v>
+        <f t="shared" si="1"/>
+        <v>46140</v>
       </c>
       <c r="B59" t="s">
         <v>3</v>
       </c>
       <c r="C59">
-        <v>6.26299999999988</v>
+        <v>6.6658999999999038</v>
       </c>
       <c r="D59">
-        <v>4.101</v>
+        <v>3.8679999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46109</v>
+        <f t="shared" si="1"/>
+        <v>46141</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60">
-        <v>6.7369000000000199</v>
+        <v>7.1683000000001007</v>
       </c>
       <c r="D60">
-        <v>4.97</v>
+        <v>4.4169999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46110</v>
+        <f t="shared" si="1"/>
+        <v>46142</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
       </c>
       <c r="C61">
-        <v>4.929700000000067</v>
+        <v>7.1614000000000182</v>
       </c>
       <c r="D61">
-        <v>3.51</v>
+        <v>4.391</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46111</v>
+        <f>A32</f>
+        <v>46113</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>7.0524000000000182</v>
+        <v>9.1120000000000019</v>
       </c>
       <c r="D62">
-        <v>5.2190000000000003</v>
+        <v>3.6448633049006207</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46112</v>
+        <f t="shared" si="1"/>
+        <v>46114</v>
       </c>
       <c r="B63" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>4.9642999999999855</v>
+        <v>11.231100000000001</v>
       </c>
       <c r="D63">
-        <v>3.5179999999999998</v>
+        <v>4.9237098511950999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46082</v>
+        <f t="shared" si="1"/>
+        <v>46115</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>9.9268000000000001</v>
       </c>
       <c r="D64">
-        <v>6.6139166666666664</v>
+        <v>4.0838164712878209</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46083</v>
+        <f t="shared" si="1"/>
+        <v>46116</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
       <c r="C65">
-        <v>16.999299999999998</v>
+        <v>12.3695</v>
       </c>
       <c r="D65">
-        <v>8.8730975049788245</v>
+        <v>5.8675497817322473</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46084</v>
+        <f t="shared" si="1"/>
+        <v>46117</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
       </c>
       <c r="C66">
-        <v>11.9626</v>
+        <v>12.860800000000001</v>
       </c>
       <c r="D66">
-        <v>5.4155638231738985</v>
+        <v>6.2647647087375233</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46085</v>
+        <f t="shared" si="1"/>
+        <v>46118</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
       <c r="C67">
-        <v>13.545399999999999</v>
+        <v>10.956200000000001</v>
       </c>
       <c r="D67">
-        <v>6.176425349215191</v>
+        <v>5.0786089528606473</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46086</v>
+        <f t="shared" si="1"/>
+        <v>46119</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>16.460100000000001</v>
+        <v>11.523500000000002</v>
       </c>
       <c r="D68">
-        <v>8.1290664978076865</v>
+        <v>5.3324322565197839</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46087</v>
+        <f t="shared" si="1"/>
+        <v>46120</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
       <c r="C69">
-        <v>12.117700000000001</v>
+        <v>10.4488</v>
       </c>
       <c r="D69">
-        <v>5.1739347873132688</v>
+        <v>4.6971320577363116</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46088</v>
+        <f t="shared" si="1"/>
+        <v>46121</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>9.2225999999999999</v>
+        <v>12.7621</v>
       </c>
       <c r="D70">
-        <v>3.576917945142212</v>
+        <v>5.7998806138032348</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46089</v>
+        <f t="shared" si="1"/>
+        <v>46122</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
       <c r="C71">
-        <v>9.287700000000001</v>
+        <v>12.3536</v>
       </c>
       <c r="D71">
-        <v>3.176253696826747</v>
+        <v>5.3265583831999992</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46090</v>
+        <f t="shared" si="1"/>
+        <v>46123</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72">
-        <v>13.533800000000001</v>
+        <v>16.174599999999998</v>
       </c>
       <c r="D72">
-        <v>6.5054274217266856</v>
+        <v>7.755072155875455</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46091</v>
+        <f t="shared" si="1"/>
+        <v>46124</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>15.081899999999999</v>
+        <v>13.578299999999999</v>
       </c>
       <c r="D73">
-        <v>7.0281211790690712</v>
+        <v>6.2730727351071831</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46092</v>
+        <f t="shared" si="1"/>
+        <v>46125</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
       <c r="C74">
-        <v>10.839</v>
+        <v>11.228500000000002</v>
       </c>
       <c r="D74">
-        <v>4.9947148531277881</v>
+        <v>5.0826818621371173</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46093</v>
+        <f t="shared" si="1"/>
+        <v>46126</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
       <c r="C75">
-        <v>7.8247999999999998</v>
+        <v>14.334999999999997</v>
       </c>
       <c r="D75">
-        <v>3.0589381603288111</v>
+        <v>6.6256841209999999</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46094</v>
+        <f t="shared" si="1"/>
+        <v>46127</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76">
-        <v>17.116599999999998</v>
+        <v>10.816799999999999</v>
       </c>
       <c r="D76">
-        <v>8.2568875891958822</v>
+        <v>4.6173861980289166</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46095</v>
+        <f t="shared" si="1"/>
+        <v>46128</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>9.3746000000000009</v>
+        <v>8.6964999999999986</v>
       </c>
       <c r="D77">
-        <v>4.1441020701577198</v>
+        <v>3.7574251117189355</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46096</v>
+        <f t="shared" si="1"/>
+        <v>46129</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>11.4382</v>
+        <v>11.281499999999998</v>
       </c>
       <c r="D78">
-        <v>5.5411459423267981</v>
+        <v>4.7495497287732196</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46097</v>
+        <f t="shared" si="1"/>
+        <v>46130</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
-        <v>14.416799999999999</v>
+        <v>14.9277</v>
       </c>
       <c r="D79">
-        <v>5.9103147116080832</v>
+        <v>6.6893338901260782</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46098</v>
+        <f t="shared" si="1"/>
+        <v>46131</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
-        <v>8.8222999999999985</v>
+        <v>15.822999999999999</v>
       </c>
       <c r="D80">
-        <v>3.6553012513431362</v>
+        <v>7.1740275924205754</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46099</v>
+        <f t="shared" si="1"/>
+        <v>46132</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81">
-        <v>13.037400000000002</v>
+        <v>12.212399999999999</v>
       </c>
       <c r="D81">
-        <v>5.4060870017868723</v>
+        <v>5.0878425225070005</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46100</v>
+        <f t="shared" si="1"/>
+        <v>46133</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
       <c r="C82">
-        <v>15.3545</v>
+        <v>12.3825</v>
       </c>
       <c r="D82">
-        <v>7.3086196551521487</v>
+        <v>5.3369417961041092</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46101</v>
+        <f t="shared" si="1"/>
+        <v>46134</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>9.8291000000000004</v>
+        <v>13.396199999999999</v>
       </c>
       <c r="D83">
-        <v>4.5896066077972337</v>
+        <v>5.9820150390267317</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46102</v>
+        <f t="shared" si="1"/>
+        <v>46135</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>12.968400000000001</v>
+        <v>16.347300000000001</v>
       </c>
       <c r="D84">
-        <v>5.155400202052661</v>
+        <v>7.1696738909824411</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46103</v>
+        <f t="shared" si="1"/>
+        <v>46136</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>9.9807000000000006</v>
+        <v>17.055099999999999</v>
       </c>
       <c r="D85">
-        <v>4.0158437333268369</v>
+        <v>7.6854815318145251</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46104</v>
+        <f t="shared" si="1"/>
+        <v>46137</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>14.171999999999999</v>
+        <v>14.284099999999999</v>
       </c>
       <c r="D86">
-        <v>5.6190060323784818</v>
+        <v>6.4653434721579099</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46105</v>
+        <f t="shared" si="1"/>
+        <v>46138</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>13.210099999999999</v>
+        <v>14.1191</v>
       </c>
       <c r="D87">
-        <v>5.4857289491118193</v>
+        <v>6.1319139993637739</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46106</v>
+        <f t="shared" si="1"/>
+        <v>46139</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>13.377400000000002</v>
+        <v>11.013500000000001</v>
       </c>
       <c r="D88">
-        <v>6.0067634834827155</v>
+        <v>4.8567013080807664</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46107</v>
+        <f t="shared" si="1"/>
+        <v>46140</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>10.6006</v>
+        <v>11.026999999999999</v>
       </c>
       <c r="D89">
-        <v>4.4510262129606293</v>
+        <v>7.1178475777699992</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46108</v>
+        <f t="shared" si="1"/>
+        <v>46141</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
       <c r="C90">
-        <v>13.253500000000003</v>
+        <v>17.778700000000001</v>
       </c>
       <c r="D90">
-        <v>5.8637483194321263</v>
+        <v>7.5324792829056531</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46109</v>
+        <f t="shared" si="1"/>
+        <v>46142</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>13.119899999999999</v>
+        <v>17.389899999999997</v>
       </c>
       <c r="D91">
-        <v>5.7940011952001669</v>
+        <v>6.9271482715755663</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46110</v>
+        <f>A62</f>
+        <v>46113</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C92">
-        <v>15.325500000000002</v>
+        <v>5.3162000000000003</v>
       </c>
       <c r="D92">
-        <v>6.0647419002004996</v>
+        <v>3.6448633049006207</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46111</v>
+        <f t="shared" si="1"/>
+        <v>46114</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93">
-        <v>15.3741</v>
+        <v>9.2858999999999998</v>
       </c>
       <c r="D93">
-        <v>7.485669972277547</v>
+        <v>4.9237098511950999</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>46112</v>
+        <f t="shared" si="1"/>
+        <v>46115</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C94">
-        <v>13.7943</v>
+        <v>9.6467999999999989</v>
       </c>
       <c r="D94">
-        <v>6.5260580991899184</v>
+        <v>4.0838164712878209</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>46082</v>
+        <f t="shared" si="1"/>
+        <v>46116</v>
       </c>
       <c r="B95" t="s">
         <v>5</v>
       </c>
       <c r="C95">
-        <v>19.052899999999998</v>
+        <v>12.7988</v>
       </c>
       <c r="D95">
-        <v>6.6139166666666664</v>
+        <v>5.8675497817322473</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>46083</v>
+        <f t="shared" si="1"/>
+        <v>46117</v>
       </c>
       <c r="B96" t="s">
         <v>5</v>
       </c>
       <c r="C96">
-        <v>16.1143</v>
+        <v>11.889899999999997</v>
       </c>
       <c r="D96">
-        <v>8.8730975049788245</v>
+        <v>6.2647647087375233</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>46084</v>
+        <f t="shared" ref="A97:A121" si="2">A67</f>
+        <v>46118</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97">
-        <v>14.558399999999999</v>
+        <v>10.260999999999999</v>
       </c>
       <c r="D97">
-        <v>5.4155638231738985</v>
+        <v>5.0786089528606473</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>46085</v>
+        <f t="shared" si="2"/>
+        <v>46119</v>
       </c>
       <c r="B98" t="s">
         <v>5</v>
       </c>
       <c r="C98">
-        <v>11.426499999999999</v>
+        <v>10.714900000000002</v>
       </c>
       <c r="D98">
-        <v>6.176425349215191</v>
+        <v>5.3324322565197839</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>46086</v>
+        <f t="shared" si="2"/>
+        <v>46120</v>
       </c>
       <c r="B99" t="s">
         <v>5</v>
       </c>
       <c r="C99">
-        <v>15.641300000000001</v>
+        <v>10.857299999999999</v>
       </c>
       <c r="D99">
-        <v>8.1290664978076865</v>
+        <v>4.6971320577363116</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>46087</v>
+        <f t="shared" si="2"/>
+        <v>46121</v>
       </c>
       <c r="B100" t="s">
         <v>5</v>
       </c>
       <c r="C100">
-        <v>12.013400000000001</v>
+        <v>13.2117</v>
       </c>
       <c r="D100">
-        <v>5.1739347873132688</v>
+        <v>5.7998806138032348</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>46088</v>
+        <f t="shared" si="2"/>
+        <v>46122</v>
       </c>
       <c r="B101" t="s">
         <v>5</v>
       </c>
       <c r="C101">
-        <v>9.011099999999999</v>
+        <v>13.785399999999999</v>
       </c>
       <c r="D101">
-        <v>3.576917945142212</v>
+        <v>5.3265583831999992</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>46089</v>
+        <f t="shared" si="2"/>
+        <v>46123</v>
       </c>
       <c r="B102" t="s">
         <v>5</v>
       </c>
       <c r="C102">
-        <v>9.8780000000000019</v>
+        <v>15.949099999999998</v>
       </c>
       <c r="D102">
-        <v>3.176253696826747</v>
+        <v>7.755072155875455</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>46090</v>
+        <f t="shared" si="2"/>
+        <v>46124</v>
       </c>
       <c r="B103" t="s">
         <v>5</v>
       </c>
       <c r="C103">
-        <v>13.864099999999999</v>
+        <v>13.703700000000001</v>
       </c>
       <c r="D103">
-        <v>6.5054274217266856</v>
+        <v>6.2730727351071831</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>46091</v>
+        <f t="shared" si="2"/>
+        <v>46125</v>
       </c>
       <c r="B104" t="s">
         <v>5</v>
       </c>
       <c r="C104">
-        <v>13.780299999999999</v>
+        <v>9.6231000000000009</v>
       </c>
       <c r="D104">
-        <v>7.0281211790690712</v>
+        <v>5.0826818621371173</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>46092</v>
+        <f t="shared" si="2"/>
+        <v>46126</v>
       </c>
       <c r="B105" t="s">
         <v>5</v>
       </c>
       <c r="C105">
-        <v>10.8461</v>
+        <v>16.5258</v>
       </c>
       <c r="D105">
-        <v>4.9947148531277881</v>
+        <v>6.6256841209999999</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>46093</v>
+        <f t="shared" si="2"/>
+        <v>46127</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106">
-        <v>6.4186999999999994</v>
+        <v>10.005499999999998</v>
       </c>
       <c r="D106">
-        <v>3.0589381603288111</v>
+        <v>4.6173861980289166</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>46094</v>
+        <f t="shared" si="2"/>
+        <v>46128</v>
       </c>
       <c r="B107" t="s">
         <v>5</v>
       </c>
       <c r="C107">
-        <v>16.528100000000002</v>
+        <v>11.2377</v>
       </c>
       <c r="D107">
-        <v>8.2568875891958822</v>
+        <v>3.7574251117189355</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>46095</v>
+        <f t="shared" si="2"/>
+        <v>46129</v>
       </c>
       <c r="B108" t="s">
         <v>5</v>
       </c>
       <c r="C108">
-        <v>7.6855999999999991</v>
+        <v>10.331700000000001</v>
       </c>
       <c r="D108">
-        <v>4.1441020701577198</v>
+        <v>4.7495497287732196</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>46096</v>
+        <f t="shared" si="2"/>
+        <v>46130</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
       </c>
       <c r="C109">
-        <v>13.225200000000001</v>
+        <v>13.948499999999999</v>
       </c>
       <c r="D109">
-        <v>5.5411459423267981</v>
+        <v>6.6893338901260782</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>46097</v>
+        <f t="shared" si="2"/>
+        <v>46131</v>
       </c>
       <c r="B110" t="s">
         <v>5</v>
       </c>
       <c r="C110">
-        <v>15.146100000000001</v>
+        <v>15.587799999999998</v>
       </c>
       <c r="D110">
-        <v>5.9103147116080832</v>
+        <v>7.1740275924205754</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>46098</v>
+        <f t="shared" si="2"/>
+        <v>46132</v>
       </c>
       <c r="B111" t="s">
         <v>5</v>
       </c>
       <c r="C111">
-        <v>8.5394999999999985</v>
+        <v>13.1736</v>
       </c>
       <c r="D111">
-        <v>3.6553012513431362</v>
+        <v>5.0878425225070005</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>46099</v>
+        <f t="shared" si="2"/>
+        <v>46133</v>
       </c>
       <c r="B112" t="s">
         <v>5</v>
       </c>
       <c r="C112">
-        <v>13.160500000000001</v>
+        <v>10.2157</v>
       </c>
       <c r="D112">
-        <v>5.4060870017868723</v>
+        <v>5.3369417961041092</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>46100</v>
+        <f t="shared" si="2"/>
+        <v>46134</v>
       </c>
       <c r="B113" t="s">
         <v>5</v>
       </c>
       <c r="C113">
-        <v>16.495000000000001</v>
+        <v>12.7403</v>
       </c>
       <c r="D113">
-        <v>7.3086196551521487</v>
+        <v>5.9820150390267317</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>46101</v>
+        <f t="shared" si="2"/>
+        <v>46135</v>
       </c>
       <c r="B114" t="s">
         <v>5</v>
       </c>
       <c r="C114">
-        <v>12.1341</v>
+        <v>15.083400000000001</v>
       </c>
       <c r="D114">
-        <v>4.5896066077972337</v>
+        <v>7.1696738909824411</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>46102</v>
+        <f t="shared" si="2"/>
+        <v>46136</v>
       </c>
       <c r="B115" t="s">
         <v>5</v>
       </c>
       <c r="C115">
-        <v>14.040099999999999</v>
+        <v>16.777200000000001</v>
       </c>
       <c r="D115">
-        <v>5.155400202052661</v>
+        <v>7.6854815318145251</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>46103</v>
+        <f t="shared" si="2"/>
+        <v>46137</v>
       </c>
       <c r="B116" t="s">
         <v>5</v>
       </c>
       <c r="C116">
-        <v>11.565799999999999</v>
+        <v>14.139199999999999</v>
       </c>
       <c r="D116">
-        <v>4.0158437333268369</v>
+        <v>6.4653434721579099</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>46104</v>
+        <f t="shared" si="2"/>
+        <v>46138</v>
       </c>
       <c r="B117" t="s">
         <v>5</v>
       </c>
       <c r="C117">
-        <v>15.823499999999999</v>
+        <v>14.969200000000001</v>
       </c>
       <c r="D117">
-        <v>5.6190060323784818</v>
+        <v>6.1319139993637739</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>46105</v>
+        <f t="shared" si="2"/>
+        <v>46139</v>
       </c>
       <c r="B118" t="s">
         <v>5</v>
       </c>
       <c r="C118">
-        <v>12.9664</v>
+        <v>13.376899999999997</v>
       </c>
       <c r="D118">
-        <v>5.4857289491118193</v>
+        <v>4.8567013080807664</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>46106</v>
+        <f t="shared" si="2"/>
+        <v>46140</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119">
-        <v>10.501100000000001</v>
+        <v>14.123899999999999</v>
       </c>
       <c r="D119">
-        <v>6.0067634834827155</v>
+        <v>7.1178475777699992</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>46107</v>
+        <f t="shared" si="2"/>
+        <v>46141</v>
       </c>
       <c r="B120" t="s">
         <v>5</v>
       </c>
       <c r="C120">
-        <v>10.4679</v>
+        <v>16.942999999999998</v>
       </c>
       <c r="D120">
-        <v>4.4510262129606293</v>
+        <v>7.5324792829056531</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>46108</v>
+        <f t="shared" si="2"/>
+        <v>46142</v>
       </c>
       <c r="B121" t="s">
         <v>5</v>
       </c>
       <c r="C121">
-        <v>13.857900000000001</v>
+        <v>17.066700000000001</v>
       </c>
       <c r="D121">
-        <v>5.8637483194321263</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
-        <v>46109</v>
-      </c>
-      <c r="B122" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122">
-        <v>14.634799999999998</v>
-      </c>
-      <c r="D122">
-        <v>5.7940011952001669</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="2">
-        <v>46110</v>
-      </c>
-      <c r="B123" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123">
-        <v>15.262099999999998</v>
-      </c>
-      <c r="D123">
-        <v>6.0647419002004996</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="2">
-        <v>46111</v>
-      </c>
-      <c r="B124" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124">
-        <v>16.677399999999999</v>
-      </c>
-      <c r="D124">
-        <v>7.485669972277547</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="2">
-        <v>46112</v>
-      </c>
-      <c r="B125" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125">
-        <v>11.387799999999999</v>
-      </c>
-      <c r="D125">
-        <v>6.5260580991899184</v>
+        <v>6.9271482715755663</v>
       </c>
     </row>
   </sheetData>
